--- a/testdata/realdata/ducts.xlsx
+++ b/testdata/realdata/ducts.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -442,6 +442,11 @@
           <t>孔数</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -469,6 +474,11 @@
           <t>4</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -496,6 +506,11 @@
           <t>4</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -523,6 +538,11 @@
           <t>4</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -550,6 +570,11 @@
           <t>4</t>
         </is>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -577,6 +602,11 @@
           <t>4</t>
         </is>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -604,6 +634,11 @@
           <t>4</t>
         </is>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -629,6 +664,11 @@
       <c r="E8" t="inlineStr">
         <is>
           <t>4</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>在网</t>
         </is>
       </c>
     </row>
